--- a/etf_holdings/2026-08-28_errors.xlsx
+++ b/etf_holdings/2026-08-28_errors.xlsx
@@ -441,24 +441,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-28 06:34:13</t>
+          <t>2026-08-28 17:25:11</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
 Call log:
-  - navigating to "https://www.etfinfo.tw/etf/00992A/holdings", waiting until "networkidle"
+  - navigating to "https://www.etfinfo.tw/etf/00403A/holdings", waiting until "networkidle"
 </t>
         </is>
       </c>
@@ -476,7 +476,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:23</t>
+          <t>2026-08-28 17:26:37</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">

--- a/etf_holdings/2026-08-28_errors.xlsx
+++ b/etf_holdings/2026-08-28_errors.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,24 +441,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:11</t>
+          <t>2026-08-28 19:07:43</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
 Call log:
-  - navigating to "https://www.etfinfo.tw/etf/00403A/holdings", waiting until "networkidle"
+  - navigating to "https://www.etfinfo.tw/etf/00985A/holdings", waiting until "networkidle"
 </t>
         </is>
       </c>
@@ -476,7 +476,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:37</t>
+          <t>2026-08-28 19:09:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -484,6 +484,56 @@
           <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
 Call log:
   - navigating to "https://www.etfinfo.tw/etf/00405A/holdings", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00407A/holdings</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-08-28 19:10:01</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
+Call log:
+  - navigating to "https://www.etfinfo.tw/etf/00407A/holdings", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-08-28 19:11:01</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
+Call log:
+  - navigating to "https://www.etfinfo.tw/etf/00993A/holdings", waiting until "networkidle"
 </t>
         </is>
       </c>

--- a/etf_holdings/2026-08-28_errors.xlsx
+++ b/etf_holdings/2026-08-28_errors.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,24 +441,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-28 19:07:43</t>
+          <t>2026-08-28 20:39:43</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
 Call log:
-  - navigating to "https://www.etfinfo.tw/etf/00985A/holdings", waiting until "networkidle"
+  - navigating to "https://www.etfinfo.tw/etf/00990A/holdings", waiting until "networkidle"
 </t>
         </is>
       </c>
@@ -466,74 +466,24 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00405A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00407A/holdings</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-28 19:09:00</t>
+          <t>2026-08-28 20:40:53</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
-Call log:
-  - navigating to "https://www.etfinfo.tw/etf/00405A/holdings", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>00407A</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00407A/holdings</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-08-28 19:10:01</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
 Call log:
   - navigating to "https://www.etfinfo.tw/etf/00407A/holdings", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2026-08-28 19:11:01</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
-Call log:
-  - navigating to "https://www.etfinfo.tw/etf/00993A/holdings", waiting until "networkidle"
 </t>
         </is>
       </c>

--- a/etf_holdings/2026-08-28_errors.xlsx
+++ b/etf_holdings/2026-08-28_errors.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,49 +441,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-28 20:39:43</t>
+          <t>2026-08-28 21:41:16</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
 Call log:
-  - navigating to "https://www.etfinfo.tw/etf/00990A/holdings", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>00407A</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00407A/holdings</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-08-28 20:40:53</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
-Call log:
-  - navigating to "https://www.etfinfo.tw/etf/00407A/holdings", waiting until "networkidle"
+  - navigating to "https://www.etfinfo.tw/etf/00403A/holdings", waiting until "networkidle"
 </t>
         </is>
       </c>
